--- a/news_daily/2026-09-16.xlsx
+++ b/news_daily/2026-09-16.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -991,6 +1015,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1161,6 +1189,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1331,6 +1363,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1501,6 +1537,10 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1663,6 +1703,10 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1825,6 +1869,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1995,6 +2043,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2157,6 +2209,10 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2327,6 +2383,10 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2497,6 +2557,10 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr"/>
+      <c r="BL11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2667,6 +2731,10 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr"/>
+      <c r="BL12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2829,6 +2897,10 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2999,6 +3071,10 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr"/>
+      <c r="BL14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3161,176 +3237,208 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>CAH</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Cardinal Health, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Cardinal Health Loses Multiple "Product Return" Lawsuits Against Pharmacy Customers and Pays Attorneys' Fees to Settle Sanctions Motion for Frivolous Litigation</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>制裁</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>'-0.941</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxNZHNLQ041NE5kX2lzbGVoLWhEVnNQY0doa0IzUUZ1UzlFbDVIV0d6MXhrWFUydEZiaFZsWEdZcTA2Y1NQcHBOU185SlI1SkQwZTJxTmotZld0WXNBNXlSZ1dYMGlrbTEyQjRIRXRiMjdzTkRYUEcybUoxQ2hVZTREQkc3ekFNQmxUaGlIbVdJYS1LMExTeEYwY3lXWjNNNjNNYnk5UnVkem9fdDV3MkhZeW5wdWZrOUk5Smo3RVJ1MlR0VDBiZzl3QXRpRkdMWE56T1FPdTRoV2k0Q2c3UW0wMGhtN3NwQ2dKZWxSVEN0TEpaMG5ITnRUR0JRdW5JLV93MDlvb1FvYlFkaV9JQzQ3bUE4Rnl2U3B4amNPeDBnQWFZTHlQc2M4UGNrdnJ1TkJKWmo0Skg4S1U?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>sanction</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>60cef94623ed4f1bb055b7f72bb0083f</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>395ddaf8402cde3df67d9a1d</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>722e72dd56227a11288533f8</t>
+        </is>
+      </c>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>'-0.941</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxNZHNLQ041NE5kX2lzbGVoLWhEVnNQY0doa0IzUUZ1UzlFbDVIV0d6MXhrWFUydEZiaFZsWEdZcTA2Y1NQcHBOU185SlI1SkQwZTJxTmotZld0WXNBNXlSZ1dYMGlrbTEyQjRIRXRiMjdzTkRYUEcybUoxQ2hVZTREQkc3ekFNQmxUaGlIbVdJYS1LMExTeEYwY3lXWjNNNjNNYnk5UnVkem9fdDV3MkhZeW5wdWZrOUk5Smo3RVJ1MlR0VDBiZzl3QXRpRkdMWE56T1FPdTRoV2k0Q2c3UW0wMGhtN3NwQ2dKZWxSVEN0TEpaMG5ITnRUR0JRdW5JLV93MDlvb1FvYlFkaV9JQzQ3bUE4Rnl2U3B4amNPeDBnQWFZTHlQc2M4UGNrdnJ1TkJKWmo0Skg4S1U?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>PR Newswire</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>SANCTION</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>sanction</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>395ddaf8402cde3df67d9a1d</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>722e72dd56227a11288533f8</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="4" t="inlineStr"/>
-      <c r="AS16" s="4" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="inlineStr">
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr"/>
+      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX16" s="4" t="inlineStr"/>
-      <c r="AY16" s="4" t="inlineStr"/>
-      <c r="AZ16" s="4" t="inlineStr"/>
-      <c r="BA16" s="4" t="inlineStr"/>
-      <c r="BB16" s="4" t="inlineStr">
+      <c r="AX16" s="3" t="inlineStr"/>
+      <c r="AY16" s="3" t="inlineStr"/>
+      <c r="AZ16" s="3" t="inlineStr"/>
+      <c r="BA16" s="3" t="inlineStr"/>
+      <c r="BB16" s="3" t="inlineStr">
         <is>
           <t>CAH</t>
         </is>
       </c>
-      <c r="BC16" s="4" t="inlineStr">
+      <c r="BC16" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="4" t="inlineStr"/>
-      <c r="BE16" s="4" t="inlineStr">
+      <c r="BD16" s="3" t="inlineStr"/>
+      <c r="BE16" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF16" s="4" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG16" s="4" t="inlineStr">
+      <c r="BG16" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3371,7 +3479,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -3381,13 +3489,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -3427,7 +3539,7 @@
       </c>
       <c r="Y17" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z17" s="4" t="inlineStr">
@@ -3436,7 +3548,11 @@
         </is>
       </c>
       <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>1fd14f26f0164efc86c61a9f652b915c</t>
+        </is>
+      </c>
       <c r="AC17" s="4" t="inlineStr">
         <is>
           <t>bc205db70e8af6acd5d2bae4</t>
@@ -3457,7 +3573,11 @@
       <c r="AL17" s="4" t="inlineStr"/>
       <c r="AM17" s="4" t="inlineStr"/>
       <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="4" t="inlineStr"/>
       <c r="AQ17" s="4" t="inlineStr"/>
       <c r="AR17" s="4" t="inlineStr"/>
@@ -3501,6 +3621,22 @@
         </is>
       </c>
       <c r="BH17" s="4" t="inlineStr"/>
+      <c r="BI17" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3551,13 +3687,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -3606,7 +3746,11 @@
         </is>
       </c>
       <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>d14e0b6a3bb8446c9f5755081398ca9a</t>
+        </is>
+      </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
           <t>a2c9bb1d20237cde49283f51</t>
@@ -3627,7 +3771,11 @@
       <c r="AL18" s="4" t="inlineStr"/>
       <c r="AM18" s="4" t="inlineStr"/>
       <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AO18" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="4" t="inlineStr"/>
       <c r="AQ18" s="4" t="inlineStr"/>
       <c r="AR18" s="4" t="inlineStr"/>
@@ -3671,6 +3819,18 @@
         </is>
       </c>
       <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3721,13 +3881,17 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -3776,7 +3940,11 @@
         </is>
       </c>
       <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr">
+        <is>
+          <t>91e5816a488044f7855b55c4234c4808</t>
+        </is>
+      </c>
       <c r="AC19" s="4" t="inlineStr">
         <is>
           <t>36670ce2603c548a0270fcbb</t>
@@ -3797,7 +3965,11 @@
       <c r="AL19" s="4" t="inlineStr"/>
       <c r="AM19" s="4" t="inlineStr"/>
       <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
+      <c r="AO19" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="4" t="inlineStr"/>
       <c r="AQ19" s="4" t="inlineStr"/>
       <c r="AR19" s="4" t="inlineStr"/>
@@ -3841,6 +4013,18 @@
         </is>
       </c>
       <c r="BH19" s="4" t="inlineStr"/>
+      <c r="BI19" s="4" t="inlineStr"/>
+      <c r="BJ19" s="4" t="inlineStr"/>
+      <c r="BK19" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4003,9 +4187,13 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH20"/>
+  <autoFilter ref="A1:BL20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4016,7 +4204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4079,6 +4267,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4380,6 +4572,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -4544,6 +4756,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4714,6 +4930,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4884,6 +5104,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5054,6 +5278,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5216,6 +5444,10 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5386,6 +5618,10 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5548,6 +5784,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5562,12 +5802,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Cardinal Health, Inc. Common Stock</t>
+          <t>Mastercard Incorporated Common Stock</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -5577,7 +5817,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Cardinal Health Loses Multiple "Product Return" Lawsuits Against Pharmacy Customers and Pays Attorneys' Fees to Settle Sanctions Motion for Frivolous Litigation</t>
+          <t>$167.5M Visa, Mastercard non-bank ATM class action settlement</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -5588,7 +5828,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>制裁</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -5598,13 +5838,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -5614,7 +5858,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>'-0.941</t>
+          <t>'-0.543</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr"/>
@@ -5628,40 +5872,44 @@
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxNZHNLQ041NE5kX2lzbGVoLWhEVnNQY0doa0IzUUZ1UzlFbDVIV0d6MXhrWFUydEZiaFZsWEdZcTA2Y1NQcHBOU185SlI1SkQwZTJxTmotZld0WXNBNXlSZ1dYMGlrbTEyQjRIRXRiMjdzTkRYUEcybUoxQ2hVZTREQkc3ekFNQmxUaGlIbVdJYS1LMExTeEYwY3lXWjNNNjNNYnk5UnVkem9fdDV3MkhZeW5wdWZrOUk5Smo3RVJ1MlR0VDBiZzl3QXRpRkdMWE56T1FPdTRoV2k0Q2c3UW0wMGhtN3NwQ2dKZWxSVEN0TEpaMG5ITnRUR0JRdW5JLV93MDlvb1FvYlFkaV9JQzQ3bUE4Rnl2U3B4amNPeDBnQWFZTHlQc2M4UGNrdnJ1TkJKWmo0Skg4S1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPUV8tNW1iOGpVMlZFV3ROZXVBRjZYYWVxSlRjNncxYXJ6Ui1YaXdrZ1V1Vzl3SC1ZM3lSWnFfZmhIT3hEZ3REV3hNUURQZFpxSEVHN3pnaFVlRGVadVNrMG93Z2oxdDVyTGlZd0JjOFZWWWhEX2tLMVVxTHNTWTByc3lJV0N3bjV5VHpUVzBlMEhKWFRSeEsxdW5ZS3FOdkh0MHVsYS1CSmpBcUJtZ1h2bW81OUtvakhpUm9GcUtBWU1ENGM1Q1Z5enVSTzdrUQ?oc=5</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Top Class Actions</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>GEOPOLITICAL</t>
+          <t>LEGAL</t>
         </is>
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>SANCTION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
         <is>
-          <t>sanction</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>1fd14f26f0164efc86c61a9f652b915c</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
-          <t>395ddaf8402cde3df67d9a1d</t>
+          <t>bc205db70e8af6acd5d2bae4</t>
         </is>
       </c>
       <c r="AD9" s="4" t="inlineStr">
         <is>
-          <t>722e72dd56227a11288533f8</t>
+          <t>8d7765995791c337aad27f12</t>
         </is>
       </c>
       <c r="AE9" s="4" t="inlineStr"/>
@@ -5674,7 +5922,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -5693,7 +5945,7 @@
       <c r="BA9" s="4" t="inlineStr"/>
       <c r="BB9" s="4" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="BC9" s="4" t="inlineStr">
@@ -5718,6 +5970,22 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -5732,12 +6000,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated Common Stock</t>
+          <t>GoDaddy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5747,7 +6015,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>$167.5M Visa, Mastercard non-bank ATM class action settlement</t>
+          <t>GDDY Shareholder Alert: GoDaddy Inc. Securities Class Action Lawsuit - Investors With Losses May Contact Levi &amp; Korsinsky</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -5758,7 +6026,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -5768,13 +6036,17 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -5784,7 +6056,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>'-0.543</t>
+          <t>'-0.427</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr"/>
@@ -5798,12 +6070,12 @@
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPUV8tNW1iOGpVMlZFV3ROZXVBRjZYYWVxSlRjNncxYXJ6Ui1YaXdrZ1V1Vzl3SC1ZM3lSWnFfZmhIT3hEZ3REV3hNUURQZFpxSEVHN3pnaFVlRGVadVNrMG93Z2oxdDVyTGlZd0JjOFZWWWhEX2tLMVVxTHNTWTByc3lJV0N3bjV5VHpUVzBlMEhKWFRSeEsxdW5ZS3FOdkh0MHVsYS1CSmpBcUJtZ1h2bW81OUtvakhpUm9GcUtBWU1ENGM1Q1Z5enVSTzdrUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQMERnWTlnUDlWR1AxZ1dKWEszbFBCUHRJdHVleExPS0tsd3pJa1NoRXlCMEV4aENxVDNoZUMxaDlpQVBOQnRiWkU2OVhJWHBleUdINDNkdVdsOFlJanRwUmpESC04V2xra2FPenliQ1M1OUU4XzR5UEx3NU1yT210WUVRTXB6cUxlQ0F5ZDZzMVZ0LWJhM1E2SGxrbFZyd0dmU1IzR29mcmNsLXN0ZjRJTWRMeEZzYTRkZ2xuR1N4OXVhZ3BXcW5GWTJ6bGJrTXE4M0ctR3h1N2g5REgtcUZYNmNBWDQ3eHozSGk5LThrY293VWhpakNYeHJWV0pyMEk5VDVZZ3d1OA?oc=5</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>Top Class Actions</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr"/>
@@ -5814,24 +6086,28 @@
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>d14e0b6a3bb8446c9f5755081398ca9a</t>
+        </is>
+      </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t>bc205db70e8af6acd5d2bae4</t>
+          <t>a2c9bb1d20237cde49283f51</t>
         </is>
       </c>
       <c r="AD10" s="4" t="inlineStr">
         <is>
-          <t>8d7765995791c337aad27f12</t>
+          <t>ab0f8f737ba4fa480c100a43</t>
         </is>
       </c>
       <c r="AE10" s="4" t="inlineStr"/>
@@ -5844,7 +6120,11 @@
       <c r="AL10" s="4" t="inlineStr"/>
       <c r="AM10" s="4" t="inlineStr"/>
       <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
+      <c r="AO10" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="4" t="inlineStr"/>
       <c r="AQ10" s="4" t="inlineStr"/>
       <c r="AR10" s="4" t="inlineStr"/>
@@ -5863,7 +6143,7 @@
       <c r="BA10" s="4" t="inlineStr"/>
       <c r="BB10" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="BC10" s="4" t="inlineStr">
@@ -5888,6 +6168,18 @@
         </is>
       </c>
       <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BI10" s="4" t="inlineStr"/>
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -5902,12 +6194,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>GoDaddy Inc. Class A Common Stock</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -5917,7 +6209,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>GDDY Shareholder Alert: GoDaddy Inc. Securities Class Action Lawsuit - Investors With Losses May Contact Levi &amp; Korsinsky</t>
+          <t>Cintas-UniFirst deal spread widens on FTC scrutiny: Bernstein</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -5928,7 +6220,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -5938,13 +6230,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -5954,7 +6250,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>'-0.427</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr"/>
@@ -5968,12 +6264,12 @@
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQMERnWTlnUDlWR1AxZ1dKWEszbFBCUHRJdHVleExPS0tsd3pJa1NoRXlCMEV4aENxVDNoZUMxaDlpQVBOQnRiWkU2OVhJWHBleUdINDNkdVdsOFlJanRwUmpESC04V2xra2FPenliQ1M1OUU4XzR5UEx3NU1yT210WUVRTXB6cUxlQ0F5ZDZzMVZ0LWJhM1E2SGxrbFZyd0dmU1IzR29mcmNsLXN0ZjRJTWRMeEZzYTRkZ2xuR1N4OXVhZ3BXcW5GWTJ6bGJrTXE4M0ctR3h1N2g5REgtcUZYNmNBWDQ3eHozSGk5LThrY293VWhpakNYeHJWV0pyMEk5VDVZZ3d1OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPOU9QdWY4TXZkUW1TTklzWVRQbDVlSGlZRkxhNDBWR0drM3d4Sk5pdkhFemYtM0ZZaXFvMlVQeGpfRDFhQ1ZTZXhTOHZGOEtBNWRZRG5fdklkRG5GTDBLeGpoVDdXbC01dGs1dnNiZU1sRTZwMzExeEZZd1pTeTRkYmktTzFFOU5jOG5oX3VEdkJmNVphSWxjMmF1ZEhUcGN1?oc=5</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr"/>
@@ -5984,24 +6280,28 @@
       </c>
       <c r="Y11" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z11" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>91e5816a488044f7855b55c4234c4808</t>
+        </is>
+      </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
-          <t>a2c9bb1d20237cde49283f51</t>
+          <t>36670ce2603c548a0270fcbb</t>
         </is>
       </c>
       <c r="AD11" s="4" t="inlineStr">
         <is>
-          <t>ab0f8f737ba4fa480c100a43</t>
+          <t>9f5ec405fcd4176d62c2d489</t>
         </is>
       </c>
       <c r="AE11" s="4" t="inlineStr"/>
@@ -6014,7 +6314,11 @@
       <c r="AL11" s="4" t="inlineStr"/>
       <c r="AM11" s="4" t="inlineStr"/>
       <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="4" t="inlineStr"/>
       <c r="AQ11" s="4" t="inlineStr"/>
       <c r="AR11" s="4" t="inlineStr"/>
@@ -6024,7 +6328,7 @@
       <c r="AV11" s="4" t="inlineStr"/>
       <c r="AW11" s="4" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX11" s="4" t="inlineStr"/>
@@ -6033,7 +6337,7 @@
       <c r="BA11" s="4" t="inlineStr"/>
       <c r="BB11" s="4" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="BC11" s="4" t="inlineStr">
@@ -6044,12 +6348,12 @@
       <c r="BD11" s="4" t="inlineStr"/>
       <c r="BE11" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG11" s="4" t="inlineStr">
@@ -6058,341 +6362,187 @@
         </is>
       </c>
       <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>CTAS</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Cintas Corporation</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Cintas-UniFirst deal spread widens on FTC scrutiny: Bernstein</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Loss of Boeing food service contract prompts 69 job cuts by vendor</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>0.258</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>'-0.953</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPOU9QdWY4TXZkUW1TTklzWVRQbDVlSGlZRkxhNDBWR0drM3d4Sk5pdkhFemYtM0ZZaXFvMlVQeGpfRDFhQ1ZTZXhTOHZGOEtBNWRZRG5fdklkRG5GTDBLeGpoVDdXbC01dGs1dnNiZU1sRTZwMzExeEZZd1pTeTRkYmktTzFFOU5jOG5oX3VEdkJmNVphSWxjMmF1ZEhUcGN1?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>36670ce2603c548a0270fcbb</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>9f5ec405fcd4176d62c2d489</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>CTAS</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNUFQ3d0ZzaXFKdkZ6YTNGVF9GY0RGTlFWMER5a1BGbjc5R2dPMFlUMjVVQ1A2ellOVWxELVlVcWgtTFpKMEQzcUVERy1vdGVaNEl6QjYxT1BlV19zVmVhSGg1bTNtaFRRNUxTRVZJSlduOUpDRmJkN3VSM1A1SE1lSnROUUFNVTh5UkZ3eDlyMVJhblBpSnF5QVZfci1OaHhJWG5tUG10ZDBEUEk?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>The Business Journals</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>job cuts</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2a48a20841c61eb1bb8796f8</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>38e460118f3553d7885c6d2b</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr"/>
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Loss of Boeing food service contract prompts 69 job cuts by vendor</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>'-0.953</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNUFQ3d0ZzaXFKdkZ6YTNGVF9GY0RGTlFWMER5a1BGbjc5R2dPMFlUMjVVQ1A2ellOVWxELVlVcWgtTFpKMEQzcUVERy1vdGVaNEl6QjYxT1BlV19zVmVhSGg1bTNtaFRRNUxTRVZJSlduOUpDRmJkN3VSM1A1SE1lSnROUUFNVTh5UkZ3eDlyMVJhblBpSnF5QVZfci1OaHhJWG5tUG10ZDBEUEk?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>The Business Journals</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>job cuts</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>2a48a20841c61eb1bb8796f8</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>38e460118f3553d7885c6d2b</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr"/>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr"/>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr"/>
-      <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr"/>
-      <c r="AM13" s="2" t="inlineStr"/>
-      <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
-      <c r="AP13" s="2" t="inlineStr"/>
-      <c r="AQ13" s="2" t="inlineStr"/>
-      <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="2" t="inlineStr"/>
-      <c r="AT13" s="2" t="inlineStr"/>
-      <c r="AU13" s="2" t="inlineStr"/>
-      <c r="AV13" s="2" t="inlineStr"/>
-      <c r="AW13" s="2" t="inlineStr"/>
-      <c r="AX13" s="2" t="inlineStr"/>
-      <c r="AY13" s="2" t="inlineStr"/>
-      <c r="AZ13" s="2" t="inlineStr"/>
-      <c r="BA13" s="2" t="inlineStr"/>
-      <c r="BB13" s="2" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="BC13" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="2" t="inlineStr"/>
-      <c r="BE13" s="2" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF13" s="2" t="inlineStr"/>
-      <c r="BG13" s="2" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr"/>
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH13"/>
+  <autoFilter ref="A1:BL12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6403,7 +6553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6466,6 +6616,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6769,9 +6923,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6782,7 +6956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6845,6 +7019,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7148,9 +7326,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7161,7 +7359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7211,134 +7409,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -7348,46 +7546,80 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="3" t="inlineStr"/>
       <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr"/>
@@ -7396,12 +7628,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -7411,90 +7643,94 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -7504,94 +7740,94 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -7599,89 +7835,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-16.xlsx
+++ b/news_daily/2026-09-16.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -89,10 +89,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -949,7 +953,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>210994bf74e74c26afad97dcc2a4562c</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>647c46d0ac1393fe493dfb1f</t>
@@ -979,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1015,864 +1027,916 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lennar Corporation Class A Common Stock</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Lennar Fiscal Q3 Adjusted Earnings, Revenue Decline</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>營運惡化</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>'-0.908</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWmNsVlFwR1hUTjBkX1o4Q2FhbWZ2VHJHb29sZWlYdmNBUFhKZXdEZnRybVh2WVVzSU12U0hObDVkcTM2bG5MZ01tckZ1ejhVZldIQlJ4cUpUQlpacGQzYzVRSjVQY0FySmo1Q1J2bmhvaHp6VEwyWDVFR0YtbGhIMnE1Q3VTVXlKUDVtOWlfU1pmQTBIMWMzcjZneGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>revenue decline</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>1195174e60c94f20b9ad3585806828f8</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>386ba1141fd10f64b4bd0ad1</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>ff424b0a675f590eef5dfdb7</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>'-0.908</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWmNsVlFwR1hUTjBkX1o4Q2FhbWZ2VHJHb29sZWlYdmNBUFhKZXdEZnRybVh2WVVzSU12U0hObDVkcTM2bG5MZ01tckZ1ejhVZldIQlJ4cUpUQlpacGQzYzVRSjVQY0FySmo1Q1J2bmhvaHp6VEwyWDVFR0YtbGhIMnE1Q3VTVXlKUDVtOWlfU1pmQTBIMWMzcjZneGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>revenue decline</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>386ba1141fd10f64b4bd0ad1</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>ff424b0a675f590eef5dfdb7</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="BC3" s="2" t="inlineStr">
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="2" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="2" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lennar Corporation Class A Common Stock</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Lennar Q3 earnings miss; guidance disappoints (LEN:NYSE)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>財報不如預期</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>'-0.953</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNdzVZanZvZUxRQmZDbnpfM1VXUGRodmtXLXFxLW96WGNJOFlhcjZ1a2p2QWtHVFhVZkpsODVkbGtaNFdWb2VlU1pvN3MtWUxSLUNzQW1tRlRCRXpxY3JVWk1LRGNHcVN6WVc5V2FQSzJ6aUFPZnhnaFl4cTZjWkJTQjJPX01CelRwWFE?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>EARNINGS_MISS</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>00fbac0b3f9a47c984651ad5407299d2</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>75e981795d579a970eb0cf3e</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>8cda12a45d54c01a2b61101c</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.953</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNdzVZanZvZUxRQmZDbnpfM1VXUGRodmtXLXFxLW96WGNJOFlhcjZ1a2p2QWtHVFhVZkpsODVkbGtaNFdWb2VlU1pvN3MtWUxSLUNzQW1tRlRCRXpxY3JVWk1LRGNHcVN6WVc5V2FQSzJ6aUFPZnhnaFl4cTZjWkJTQjJPX01CelRwWFE?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>75e981795d579a970eb0cf3e</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>8cda12a45d54c01a2b61101c</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>USB</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>U.S. Bancorp Common Stock</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>U.S. Bancorp (USB) Shares Fall 4.0% -- What GF Score of 75 Tells Investors</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>'-0.963</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>原始代號與公司名稱交叉核對</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQT0F5Q3l1TWxGdElfMF9WV3NYUWpFNWdVT0V3OTRYcDUzUHVacVFSUGlqM05PUmpwV0JvUWFWNGFRTURsQmxkb2xISTRZdmk3M2gwTlJESlNSNWVHUnhtUERvVUhfdHFKaUJWVlM2ZEFldEU1M1JKTnRLMFI0ZjRNdzdQdDc1cEt3VVQxcnIzS1pkc3NraXlJUWVfRk9JdDRwRHN2Qllfcw?oc=5</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>GuruFocus</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>69ac0dfea689632ddfab2004</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>77483832370c84271a707cde</t>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>USB</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr"/>
-      <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>JBHT</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>J.B. Hunt</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>J.B. Hunt shares fall Wednesday after company warns of third quarter profit decline</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>'-0.961</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNU0s5SnRFNlRmNUxmOG94SlJmLVRWMmdzTWRrMTVIZ1hmSGllT055eXNwTUc4MnNqRC1UMGNtSWxuUXFqd2JjQzNJZkhwcFBZZGtfV0Y3TmZPSVRoUzVGV3BWR2d0WGFvWkpzN2RQZm41cHNpM3RLa2lNaUNRS0VKYWF3RTNIWlBFTGpUR2dmRVdsWnNvUFc5S3VHOXlrYlU?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>The Arkansas Democrat-Gazette</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>84273e6232ffb2e6c160a765</t>
         </is>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
+      <c r="AD6" s="2" t="inlineStr">
         <is>
           <t>e98bc148db818721a897e1d9</t>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr"/>
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>JBHT</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr"/>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr"/>
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Boeing</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Boeing Stock Skids As CEO Warns Of Further 737 Production Delays</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>生產延遲</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>'-0.951</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNQjBrOG1aMjJPLVBMUlpuZF9ibjhuREhCZnVXNWhrUGVTOGZkT093UmgwdTlxMmVaNWtNM181SURMRDFKTlFiU2xLa1JWSDVBUFZHYlRhQ3RIN1dzN1l6VktBNHItN2pZa3dSc1ZEQnktRHl1ekxCLXdrWVc3aDNiUVQxT050Q0VwaElaTU5GaWdVUQ?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Investor's Business Daily</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>PRODUCTION_DELAY</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>production delay</t>
         </is>
       </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>0998e76fe0a705ea0c65818e</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="inlineStr">
+      <c r="AD7" s="2" t="inlineStr">
         <is>
           <t>7d12c75627d506018a7fc517</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr"/>
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr"/>
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1908,28 +1972,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>營運惡化</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1969,7 +2037,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>OPERATING_DETERIORATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1978,7 +2046,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>4237e19c8c6240769f1f8f9f22583d5d</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>13ccdefbbd3b0d1f94719e11</t>
@@ -1999,7 +2071,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2043,698 +2119,710 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Coinbase and Strategy Shares Fall After Senate Blocks Digital Asset Bill</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>'-0.947</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQNmdqT1Z5eUdTeE1CT2c2OE16Z2FINV9TNDU1UHg4bjJPUWstWUFDdGdybVJtdW9pc0FCaFRka3VxcGVlZWVYeW44TmR5bElDMEpDZGhlSjVqNlFxVFBiaEJPa0dvQy11d3U3Vl83MnJfYURkdTNjS3FqclJOQjFjTWM0QmtiSnZQTmtBMzIycFJvSWZXeERmUV9tazlBZ19rVkRr?oc=5</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>cbf5bb9817c420c29f32a86c</t>
         </is>
       </c>
-      <c r="AD9" s="3" t="inlineStr">
+      <c r="AD9" s="2" t="inlineStr">
         <is>
           <t>bdc8c237e4bf49642c1dbdba</t>
         </is>
       </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr"/>
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BF9" s="2" t="inlineStr"/>
+      <c r="BG9" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Edison International Common Stock</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Fitch cuts Edison International outlook on wildfire reform stall</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>'-0.462</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQU0w0dkdkRjBaMUxoWWZwNzBsZjg2bFItak5sSzBmNFZrVTJON2UzZmI4alFwbDEwVlV3cGlicXdFc3RLeU9HS2N3TnV4aW50cF9Ta01DRGpNd1Z1ZzdydGZZRzI5QjVYeGhPcHJXX3hNX3BpLUlla0VsSlR3ZnJzYW01MHdScW82U0s1MzlkeVJCOFh6VDdSQm5pYktlcU5sWTBtNUJXMUV0cTZhVklJRmVzem9DLVdyOWRmdTk2OE0wbnhK?oc=5</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Investing.com</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>wildfire</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>6989881c6c1300785a06d419</t>
         </is>
       </c>
-      <c r="AD10" s="3" t="inlineStr">
+      <c r="AD10" s="2" t="inlineStr">
         <is>
           <t>bcedb6c9cb5415d5e2d85260</t>
         </is>
       </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>LIN</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Linde plc</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Linde (LIN) Stock Could Be 50% Overvalued On Cash Flow Estimates</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>'-0.076</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYlNfWjlVWjh1bFJlamRrMVlyNDhDX1lXS0p1NGVJWFZTdk9tMXV2OWNoZzBZdlgtMnB6YlFaU0pRNXNwQVdhUzBmTmEzUWZfc0FUcmRnX3NjemNCZkRxNWFEbmFZWXpfbG5aZ3lzbEJvWURSMWd5M01SNWNfNkI2WDZrdGU2NzNUbjJQeVZaZTFPeFhia05vR2hVdkRiS3hlYU9tWUJZWFBDUEZkLXBXaERHMnFWck40aTFCb0xPMXl3Z9IBxwFBVV95cUxNSTBrUlJvYlFLaC11RFFGellyMUFmVVBpcnljek5nNXVuNEU0SlZjbm0wTEI5OGdlMy1jbThUYXQxUmNBMkdDZVFIZlhJRklkWEwzWG9BUWc1REM1Wkk1d291SzRCVEp0cEU2Y0xlV2RGVkdndjBqSDlZUTJMcm9EMEpSRm0yTC1pQU9sZy1zR1ZaOVJDa0t5NXN5N2IwQkdaRzdlSE02MVU2eUxuQU1ZYk9hVGRJbDJZaUI3dHFtd2VzaGhTOGlj?oc=5</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Simply Wall Street</t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>7183580156bff63adc613a7c</t>
         </is>
       </c>
-      <c r="AD11" s="3" t="inlineStr">
+      <c r="AD11" s="2" t="inlineStr">
         <is>
           <t>205119551f8026ceca0d0ebf</t>
         </is>
       </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AP11" s="2" t="inlineStr"/>
+      <c r="AQ11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="inlineStr"/>
+      <c r="AS11" s="2" t="inlineStr"/>
+      <c r="AT11" s="2" t="inlineStr"/>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
+      <c r="AX11" s="2" t="inlineStr"/>
+      <c r="AY11" s="2" t="inlineStr"/>
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr"/>
+      <c r="BB11" s="2" t="inlineStr">
         <is>
           <t>LIN</t>
         </is>
       </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="BC11" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="2" t="inlineStr"/>
+      <c r="BE11" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BG11" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>TER</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Teradyne, Inc.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Teradyne (TER) Stock Could Be 39% Overvalued Despite Fresh AI Demand News</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0.819</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPemE0V3pUdWFOZC16ZVA3Rzl4LUN2UTAyS1dPdzNkWWdxT1JKQVhKWlVsY3RXUklsdlBNWkt4amhBRXU1Q3BaeFljVWRmMnJncEg5TmlwSGVNYWxzdG5MYUM0TnRKaV9EUXJKY3VrNndVZmdxZ2VRNFVqenBNb0xTSEVHNkEtX2RyVURrMmNOWVU0ZmJzaVNPTEZKdmlrOFNaT003Y1k4cE55Uk5pS2dvd3BKLV9hcnlFeV81TlFlaXJrQm9jRVpkcklUcEHSAdIBQVVfeXFMTmtpS2RWckRwMzY1V3VGT0t2R0E0RU5PaW45UkNvNU96ZHl3TjhVSExtZWo5VUV1SUZtOVhDVE84ajJHQzM2NmgtVF9nZHgxY1Zod0txMl9SaTdTN05ZTnJzNy16X1l4emwwTmE5NFJ5ejZNYXpwNkNtTHlvT25zWUd2Vm4ydGkyR0FZTmxRSXAzTEtMdDZINThIbmpDNTYyNWM5MFpBNUM0Q2haWEtWMnRKVF9yVFhwR2Yzd0tnS1E3QkU0aENXMDVKVEJIMEdITm9R?oc=5</t>
         </is>
       </c>
-      <c r="V12" s="3" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Simply Wall Street</t>
         </is>
       </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z12" s="3" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>4aa27d71cd719180b7b6a112</t>
         </is>
       </c>
-      <c r="AD12" s="3" t="inlineStr">
+      <c r="AD12" s="2" t="inlineStr">
         <is>
           <t>7f0d7822dae3681f790f294e</t>
         </is>
       </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>TER</t>
         </is>
       </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2770,28 +2858,32 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2831,7 +2923,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2840,7 +2932,11 @@
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>49d5ebec992e4e418f4cda8570c4850e</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>b29d42c1c059afa5b0c2aa80</t>
@@ -2861,7 +2957,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -2897,10 +2997,22 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
-      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2936,28 +3048,32 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2997,7 +3113,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -3006,7 +3122,11 @@
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>01a001c997a8481992b35869347c6cf9</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>647c46d0ac1393fe493dfb1f</t>
@@ -3027,7 +3147,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3071,10 +3195,22 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
-      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3110,28 +3246,32 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3171,7 +3311,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -3180,7 +3320,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>922d7f6f9f42470d8dd65435ce85a137</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>6af28d1c312b51872fa73cb0</t>
@@ -3201,7 +3345,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3237,204 +3385,216 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>CAH</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Cardinal Health, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Cardinal Health Loses Multiple "Product Return" Lawsuits Against Pharmacy Customers and Pays Attorneys' Fees to Settle Sanctions Motion for Frivolous Litigation</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>'-0.941</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxNZHNLQ041NE5kX2lzbGVoLWhEVnNQY0doa0IzUUZ1UzlFbDVIV0d6MXhrWFUydEZiaFZsWEdZcTA2Y1NQcHBOU185SlI1SkQwZTJxTmotZld0WXNBNXlSZ1dYMGlrbTEyQjRIRXRiMjdzTkRYUEcybUoxQ2hVZTREQkc3ekFNQmxUaGlIbVdJYS1LMExTeEYwY3lXWjNNNjNNYnk5UnVkem9fdDV3MkhZeW5wdWZrOUk5Smo3RVJ1MlR0VDBiZzl3QXRpRkdMWE56T1FPdTRoV2k0Q2c3UW0wMGhtN3NwQ2dKZWxSVEN0TEpaMG5ITnRUR0JRdW5JLV93MDlvb1FvYlFkaV9JQzQ3bUE4Rnl2U3B4amNPeDBnQWFZTHlQc2M4UGNrdnJ1TkJKWmo0Skg4S1U?oc=5</t>
         </is>
       </c>
-      <c r="V16" s="3" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>PR Newswire</t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>GEOPOLITICAL</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>sanction</t>
         </is>
       </c>
-      <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>60cef94623ed4f1bb055b7f72bb0083f</t>
         </is>
       </c>
-      <c r="AC16" s="3" t="inlineStr">
+      <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>395ddaf8402cde3df67d9a1d</t>
         </is>
       </c>
-      <c r="AD16" s="3" t="inlineStr">
+      <c r="AD16" s="2" t="inlineStr">
         <is>
           <t>722e72dd56227a11288533f8</t>
         </is>
       </c>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="inlineStr"/>
-      <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr">
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
+      <c r="AL16" s="2" t="inlineStr"/>
+      <c r="AM16" s="2" t="inlineStr"/>
+      <c r="AN16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr">
+      <c r="AP16" s="2" t="inlineStr"/>
+      <c r="AQ16" s="2" t="inlineStr"/>
+      <c r="AR16" s="2" t="inlineStr"/>
+      <c r="AS16" s="2" t="inlineStr"/>
+      <c r="AT16" s="2" t="inlineStr"/>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX16" s="3" t="inlineStr"/>
-      <c r="AY16" s="3" t="inlineStr"/>
-      <c r="AZ16" s="3" t="inlineStr"/>
-      <c r="BA16" s="3" t="inlineStr"/>
-      <c r="BB16" s="3" t="inlineStr">
+      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AY16" s="2" t="inlineStr"/>
+      <c r="AZ16" s="2" t="inlineStr"/>
+      <c r="BA16" s="2" t="inlineStr"/>
+      <c r="BB16" s="2" t="inlineStr">
         <is>
           <t>CAH</t>
         </is>
       </c>
-      <c r="BC16" s="3" t="inlineStr">
+      <c r="BC16" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="3" t="inlineStr"/>
-      <c r="BE16" s="3" t="inlineStr">
+      <c r="BD16" s="2" t="inlineStr"/>
+      <c r="BE16" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BG16" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH16" s="3" t="inlineStr"/>
-      <c r="BI16" s="3" t="inlineStr">
+      <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ16" s="3" t="inlineStr"/>
-      <c r="BK16" s="3" t="inlineStr">
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL16" s="3" t="inlineStr">
+      <c r="BL16" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -4060,28 +4220,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4121,7 +4285,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4130,7 +4294,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>f8139b507b964d2da0915388b5ed6a20</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>2a48a20841c61eb1bb8796f8</t>
@@ -4151,7 +4319,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4187,10 +4359,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL20"/>
@@ -4204,7 +4388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL12"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4596,1953 +4780,981 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>ZBH</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Zimmer Biomet</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Lennar Corporation Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Medtronic taps Zimmer Biomet executive as its new supply chain VP</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Lennar Fiscal Q3 Adjusted Earnings, Revenue Decline</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>'-0.908</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWmNsVlFwR1hUTjBkX1o4Q2FhbWZ2VHJHb29sZWlYdmNBUFhKZXdEZnRybVh2WVVzSU12U0hObDVkcTM2bG5MZ01tckZ1ejhVZldIQlJ4cUpUQlpacGQzYzVRSjVQY0FySmo1Q1J2bmhvaHp6VEwyWDVFR0YtbGhIMnE1Q3VTVXlKUDVtOWlfU1pmQTBIMWMzcjZneGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>revenue decline</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>1195174e60c94f20b9ad3585806828f8</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>386ba1141fd10f64b4bd0ad1</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>ff424b0a675f590eef5dfdb7</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOdzhLWmRnMWtfRlhFbVE4SG51WFprbFRmeWpPTWRjMlZ6cFBRRTQ5QzRKdjFCMWlBUEU5ME0xUmlwQzBmQXJJZ2tlZ1RmVnp5emttZHlGRE0tdnR2MkczQlE1bDg2dlRVWlc3d2tJUFZFSzBsZXJYZDluRzA0MzVvUGpFVHVTdkZXYUtUTlZDNkhITkpPRkl0SFdYS3BHTGd0d1dtazFRWjlkdGpsbC1N?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Medical Design &amp; Outsourcing</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>647c46d0ac1393fe493dfb1f</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>ab811a61cbf13525254328ae</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>ZBH</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lennar Corporation Class A Common Stock</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Lennar Fiscal Q3 Adjusted Earnings, Revenue Decline</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Lennar Q3 earnings miss; guidance disappoints (LEN:NYSE)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>財報不如預期</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>'-0.953</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNdzVZanZvZUxRQmZDbnpfM1VXUGRodmtXLXFxLW96WGNJOFlhcjZ1a2p2QWtHVFhVZkpsODVkbGtaNFdWb2VlU1pvN3MtWUxSLUNzQW1tRlRCRXpxY3JVWk1LRGNHcVN6WVc5V2FQSzJ6aUFPZnhnaFl4cTZjWkJTQjJPX01CelRwWFE?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>EARNINGS_MISS</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>00fbac0b3f9a47c984651ad5407299d2</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>75e981795d579a970eb0cf3e</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>8cda12a45d54c01a2b61101c</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>'-0.908</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWmNsVlFwR1hUTjBkX1o4Q2FhbWZ2VHJHb29sZWlYdmNBUFhKZXdEZnRybVh2WVVzSU12U0hObDVkcTM2bG5MZ01tckZ1ejhVZldIQlJ4cUpUQlpacGQzYzVRSjVQY0FySmo1Q1J2bmhvaHp6VEwyWDVFR0YtbGhIMnE1Q3VTVXlKUDVtOWlfU1pmQTBIMWMzcjZneGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>revenue decline</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>386ba1141fd10f64b4bd0ad1</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>ff424b0a675f590eef5dfdb7</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="BC3" s="2" t="inlineStr">
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="2" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="2" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>LEN</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Lennar Corporation Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated Common Stock</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Lennar Q3 earnings miss; guidance disappoints (LEN:NYSE)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>$167.5M Visa, Mastercard non-bank ATM class action settlement</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.543</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPUV8tNW1iOGpVMlZFV3ROZXVBRjZYYWVxSlRjNncxYXJ6Ui1YaXdrZ1V1Vzl3SC1ZM3lSWnFfZmhIT3hEZ3REV3hNUURQZFpxSEVHN3pnaFVlRGVadVNrMG93Z2oxdDVyTGlZd0JjOFZWWWhEX2tLMVVxTHNTWTByc3lJV0N3bjV5VHpUVzBlMEhKWFRSeEsxdW5ZS3FOdkh0MHVsYS1CSmpBcUJtZ1h2bW81OUtvakhpUm9GcUtBWU1ENGM1Q1Z5enVSTzdrUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>1fd14f26f0164efc86c61a9f652b915c</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>bc205db70e8af6acd5d2bae4</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>8d7765995791c337aad27f12</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr"/>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.953</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNdzVZanZvZUxRQmZDbnpfM1VXUGRodmtXLXFxLW96WGNJOFlhcjZ1a2p2QWtHVFhVZkpsODVkbGtaNFdWb2VlU1pvN3MtWUxSLUNzQW1tRlRCRXpxY3JVWk1LRGNHcVN6WVc5V2FQSzJ6aUFPZnhnaFl4cTZjWkJTQjJPX01CelRwWFE?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>75e981795d579a970eb0cf3e</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>8cda12a45d54c01a2b61101c</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>LEN</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>CAH</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Cardinal Health, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc. Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Can CAH Navigate IRA Pricing Changes Risk Without Margin Pressure?</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>GDDY Shareholder Alert: GoDaddy Inc. Securities Class Action Lawsuit - Investors With Losses May Contact Levi &amp; Korsinsky</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>'-0.427</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQMERnWTlnUDlWR1AxZ1dKWEszbFBCUHRJdHVleExPS0tsd3pJa1NoRXlCMEV4aENxVDNoZUMxaDlpQVBOQnRiWkU2OVhJWHBleUdINDNkdVdsOFlJanRwUmpESC04V2xra2FPenliQ1M1OUU4XzR5UEx3NU1yT210WUVRTXB6cUxlQ0F5ZDZzMVZ0LWJhM1E2SGxrbFZyd0dmU1IzR29mcmNsLXN0ZjRJTWRMeEZzYTRkZ2xuR1N4OXVhZ3BXcW5GWTJ6bGJrTXE4M0ctR3h1N2g5REgtcUZYNmNBWDQ3eHozSGk5LThrY293VWhpakNYeHJWV0pyMEk5VDVZZ3d1OA?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>d14e0b6a3bb8446c9f5755081398ca9a</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>a2c9bb1d20237cde49283f51</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>ab0f8f737ba4fa480c100a43</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0.197</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNLVI5ZUxIYnY3SjlJVEI5SEZrZkE4dWM4RjVsNGNRbVlDUDZ1MjZRbF9IZC1STkJoazJvRnhSb0kyUGdaMGxJUEduMWxDTlBIak1YbHRSbzJUSXlaTmlUbTBnTjRCaUtxMkgwelBBMlJxMlQzYjhpYjM1VlpJS0x6cnpBMjlDWGt3NGJid3owTEg3R2N2U085TQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>13ccdefbbd3b0d1f94719e11</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>69fe4dfd13e8c130ffbb70cd</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr">
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>CAH</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr">
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="2" t="inlineStr">
+      <c r="BF5" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="2" t="inlineStr">
+      <c r="BG5" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
-      <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cintas Corporation</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Boeing parts ways with food service provider Aramark, 69 layoffs planned</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Cintas-UniFirst deal spread widens on FTC scrutiny: Bernstein</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0.258</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPOU9QdWY4TXZkUW1TTklzWVRQbDVlSGlZRkxhNDBWR0drM3d4Sk5pdkhFemYtM0ZZaXFvMlVQeGpfRDFhQ1ZTZXhTOHZGOEtBNWRZRG5fdklkRG5GTDBLeGpoVDdXbC01dGs1dnNiZU1sRTZwMzExeEZZd1pTeTRkYmktTzFFOU5jOG5oX3VEdkJmNVphSWxjMmF1ZEhUcGN1?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>91e5816a488044f7855b55c4234c4808</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>36670ce2603c548a0270fcbb</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>9f5ec405fcd4176d62c2d489</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.949</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNUjZCNl9Sb1FEOGtwMlNvWXBYZW1sZm5zUWRpbEVaU3F6cmlJRk5RbmJmeUVEQm42RE9tOWVXRlhDOUNydVBUT1AzNGtTVlI3bWN4YnBmZ3RLcXJrM2hYX1dvMVNWdzhhUE9RdzQ5VVkydUQzWURFblNnYTVCaGstLVdydnRWQk5RVnFDZ2xuN2JNSnB5ZHZHb1FCbDRONnk2eHhZRE5DMjNJd9IBrwFBVV95cUxPN19TaVJEbGtBQ2p3cmFUZ0QtQjJJeDhwYU1SMkczblBaVmt0U2xCeFdWU25LUlU1TVh1TnByWHdXXzRMZmVONlZ3UTg5M0cyMU10OFFfUzFQcFNEcWFvLXJXQV9uQTR6YVNTQk54c0lvMFZpaS04SFZtbDJ2WTBkRFB4Q2F3WTRIVHhfT2ZMOXVRWXhweGNsalliWEwxUzd1dUs0V0U1MldZdGxvUlpv?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>FOX 2</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>b29d42c1c059afa5b0c2aa80</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>d4c61406433c67429708d4d2</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr"/>
-      <c r="BG6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Medtronic plc. Ordinary Shares</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Medtronic taps Zimmer Biomet executive as its new supply chain VP</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOdzhLWmRnMWtfRlhFbVE4SG51WFprbFRmeWpPTWRjMlZ6cFBRRTQ5QzRKdjFCMWlBUEU5ME0xUmlwQzBmQXJJZ2tlZ1RmVnp5emttZHlGRE0tdnR2MkczQlE1bDg2dlRVWlc3d2tJUFZFSzBsZXJYZDluRzA0MzVvUGpFVHVTdkZXYUtUTlZDNkhITkpPRkl0SFdYS3BHTGd0d1dtazFRWjlkdGpsbC1N?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Medical Design &amp; Outsourcing</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>647c46d0ac1393fe493dfb1f</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>bf5e9b02165db040da90734f</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr"/>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="inlineStr"/>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
-      <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="inlineStr"/>
-      <c r="AT7" s="2" t="inlineStr"/>
-      <c r="AU7" s="2" t="inlineStr"/>
-      <c r="AV7" s="2" t="inlineStr"/>
-      <c r="AW7" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="2" t="inlineStr"/>
-      <c r="AY7" s="2" t="inlineStr"/>
-      <c r="AZ7" s="2" t="inlineStr"/>
-      <c r="BA7" s="2" t="inlineStr"/>
-      <c r="BB7" s="2" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="BC7" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="2" t="inlineStr"/>
-      <c r="BE7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="2" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
-      <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Cooper Companies (The)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Good Culture names COO to scale supply chain</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0.201</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPckdjQVhwQV9weXk2YWU5d2hqYWdBZzRjS3NMbG5rQTMtcmo1MlJsU1VBdTY3WFFwOGd6X0N6c05iSGZPajQ4dElrUmcxcUxvRlBfUHZCdF9mUWVhekRPcWdmWnRUQnZkUWpIWWt4ODZkdW9PS09mY2ZQZGZHS1UyWDVTRTJ1R2hTakNualNxc3ZTRzQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Supply Chain Dive</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>6af28d1c312b51872fa73cb0</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>cea31d320d845d82bae05a7f</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr"/>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr"/>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="inlineStr"/>
-      <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
-      <c r="AP8" s="2" t="inlineStr"/>
-      <c r="AQ8" s="2" t="inlineStr"/>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr"/>
-      <c r="AT8" s="2" t="inlineStr"/>
-      <c r="AU8" s="2" t="inlineStr"/>
-      <c r="AV8" s="2" t="inlineStr"/>
-      <c r="AW8" s="2" t="inlineStr"/>
-      <c r="AX8" s="2" t="inlineStr"/>
-      <c r="AY8" s="2" t="inlineStr"/>
-      <c r="AZ8" s="2" t="inlineStr"/>
-      <c r="BA8" s="2" t="inlineStr"/>
-      <c r="BB8" s="2" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="BC8" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="2" t="inlineStr"/>
-      <c r="BE8" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="2" t="inlineStr"/>
-      <c r="BG8" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
-      <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated Common Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>$167.5M Visa, Mastercard non-bank ATM class action settlement</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>'-0.543</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPUV8tNW1iOGpVMlZFV3ROZXVBRjZYYWVxSlRjNncxYXJ6Ui1YaXdrZ1V1Vzl3SC1ZM3lSWnFfZmhIT3hEZ3REV3hNUURQZFpxSEVHN3pnaFVlRGVadVNrMG93Z2oxdDVyTGlZd0JjOFZWWWhEX2tLMVVxTHNTWTByc3lJV0N3bjV5VHpUVzBlMEhKWFRSeEsxdW5ZS3FOdkh0MHVsYS1CSmpBcUJtZ1h2bW81OUtvakhpUm9GcUtBWU1ENGM1Q1Z5enVSTzdrUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr">
-        <is>
-          <t>1fd14f26f0164efc86c61a9f652b915c</t>
-        </is>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>bc205db70e8af6acd5d2bae4</t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t>8d7765995791c337aad27f12</t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="BC9" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="4" t="inlineStr"/>
-      <c r="BI9" s="4" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr">
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL9" s="4" t="inlineStr">
+      <c r="BL6" s="4" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>GDDY</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>GoDaddy Inc. Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>GDDY Shareholder Alert: GoDaddy Inc. Securities Class Action Lawsuit - Investors With Losses May Contact Levi &amp; Korsinsky</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>'-0.427</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQMERnWTlnUDlWR1AxZ1dKWEszbFBCUHRJdHVleExPS0tsd3pJa1NoRXlCMEV4aENxVDNoZUMxaDlpQVBOQnRiWkU2OVhJWHBleUdINDNkdVdsOFlJanRwUmpESC04V2xra2FPenliQ1M1OUU4XzR5UEx3NU1yT210WUVRTXB6cUxlQ0F5ZDZzMVZ0LWJhM1E2SGxrbFZyd0dmU1IzR29mcmNsLXN0ZjRJTWRMeEZzYTRkZ2xuR1N4OXVhZ3BXcW5GWTJ6bGJrTXE4M0ctR3h1N2g5REgtcUZYNmNBWDQ3eHozSGk5LThrY293VWhpakNYeHJWV0pyMEk5VDVZZ3d1OA?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr">
-        <is>
-          <t>d14e0b6a3bb8446c9f5755081398ca9a</t>
-        </is>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>a2c9bb1d20237cde49283f51</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>ab0f8f737ba4fa480c100a43</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
-        <is>
-          <t>GDDY</t>
-        </is>
-      </c>
-      <c r="BC10" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH10" s="4" t="inlineStr"/>
-      <c r="BI10" s="4" t="inlineStr"/>
-      <c r="BJ10" s="4" t="inlineStr"/>
-      <c r="BK10" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>CTAS</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Cintas Corporation</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Cintas-UniFirst deal spread widens on FTC scrutiny: Bernstein</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>0.258</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPOU9QdWY4TXZkUW1TTklzWVRQbDVlSGlZRkxhNDBWR0drM3d4Sk5pdkhFemYtM0ZZaXFvMlVQeGpfRDFhQ1ZTZXhTOHZGOEtBNWRZRG5fdklkRG5GTDBLeGpoVDdXbC01dGs1dnNiZU1sRTZwMzExeEZZd1pTeTRkYmktTzFFOU5jOG5oX3VEdkJmNVphSWxjMmF1ZEhUcGN1?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>91e5816a488044f7855b55c4234c4808</t>
-        </is>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>36670ce2603c548a0270fcbb</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>9f5ec405fcd4176d62c2d489</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>CTAS</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH11" s="4" t="inlineStr"/>
-      <c r="BI11" s="4" t="inlineStr"/>
-      <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Loss of Boeing food service contract prompts 69 job cuts by vendor</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>'-0.953</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNUFQ3d0ZzaXFKdkZ6YTNGVF9GY0RGTlFWMER5a1BGbjc5R2dPMFlUMjVVQ1A2ellOVWxELVlVcWgtTFpKMEQzcUVERy1vdGVaNEl6QjYxT1BlV19zVmVhSGg1bTNtaFRRNUxTRVZJSlduOUpDRmJkN3VSM1A1SE1lSnROUUFNVTh5UkZ3eDlyMVJhblBpSnF5QVZfci1OaHhJWG5tUG10ZDBEUEk?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>The Business Journals</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>job cuts</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>2a48a20841c61eb1bb8796f8</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>38e460118f3553d7885c6d2b</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr"/>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="BC12" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="2" t="inlineStr"/>
-      <c r="BE12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF12" s="2" t="inlineStr"/>
-      <c r="BG12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
-      <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL12"/>
+  <autoFilter ref="A1:BL6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7529,645 +6741,645 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-26</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H2" s="3" t="b">
+      <c r="H2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:23:38.366332+08:00</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:40:53.776257+08:00</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="2" t="n">
         <v>1926</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="P2" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1976</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="W2" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-25</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H3" s="3" t="b">
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:23:17.137147+08:00</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:40:12.120180+08:00</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="2" t="n">
         <v>2032</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2089</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="W3" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="X3" s="3" t="inlineStr"/>
-      <c r="Y3" s="3" t="inlineStr"/>
-      <c r="Z3" s="3" t="inlineStr"/>
-      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-24</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H4" s="3" t="b">
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T12:44:09.884829+08:00</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T13:04:34.984103+08:00</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="2" t="n">
         <v>3760</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="P4" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="2" t="n">
         <v>3802</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="2" t="n">
         <v>3825</v>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="2" t="n">
         <v>3793</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
-      <c r="Z4" s="3" t="inlineStr"/>
-      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296780+08:00</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296790+08:00</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="n">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
         <v>1691</v>
       </c>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr"/>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="n">
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-10-22T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="b">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:34.299718+08:00</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:32:11.776786+08:00</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="3" t="inlineStr"/>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
-      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H7" s="3" t="b">
+      <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:20:47.845317+08:00</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:21:20.302846+08:00</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="P7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H8" s="3" t="b">
+      <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA8"/>

--- a/news_daily/2026-09-16.xlsx
+++ b/news_daily/2026-09-16.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -1466,28 +1466,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1536,7 +1540,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>ff0e5c4dfdb04eaa86739ce500d1beaf</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>69ac0dfea689632ddfab2004</t>
@@ -1557,7 +1565,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1601,176 +1613,212 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>JBHT</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>J.B. Hunt</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>J.B. Hunt shares fall Wednesday after company warns of third quarter profit decline</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>股價下跌</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>財測下修</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>'-0.961</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNU0s5SnRFNlRmNUxmOG94SlJmLVRWMmdzTWRrMTVIZ1hmSGllT055eXNwTUc4MnNqRC1UMGNtSWxuUXFqd2JjQzNJZkhwcFBZZGtfV0Y3TmZPSVRoUzVGV3BWR2d0WGFvWkpzN2RQZm41cHNpM3RLa2lNaUNRS0VKYWF3RTNIWlBFTGpUR2dmRVdsWnNvUFc5S3VHOXlrYlU?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>The Arkansas Democrat-Gazette</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>EARNINGS_WARNING</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>shares fall</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>b4977753ed5542b089475074f455ecd4</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>84273e6232ffb2e6c160a765</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>e98bc148db818721a897e1d9</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.961</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNU0s5SnRFNlRmNUxmOG94SlJmLVRWMmdzTWRrMTVIZ1hmSGllT055eXNwTUc4MnNqRC1UMGNtSWxuUXFqd2JjQzNJZkhwcFBZZGtfV0Y3TmZPSVRoUzVGV3BWR2d0WGFvWkpzN2RQZm41cHNpM3RLa2lNaUNRS0VKYWF3RTNIWlBFTGpUR2dmRVdsWnNvUFc5S3VHOXlrYlU?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>The Arkansas Democrat-Gazette</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_MOVEMENT</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>shares fall</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>84273e6232ffb2e6c160a765</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>e98bc148db818721a897e1d9</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>JBHT</t>
         </is>
       </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF6" s="2" t="inlineStr"/>
-      <c r="BG6" s="2" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1821,13 +1869,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1876,7 +1928,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>86b5ee054e4045adb53008305376b8ff</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>0998e76fe0a705ea0c65818e</t>
@@ -1897,7 +1953,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1935,8 +1995,16 @@
       <c r="BH7" s="2" t="inlineStr"/>
       <c r="BI7" s="2" t="inlineStr"/>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2170,28 +2238,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2231,7 +2303,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2240,7 +2312,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>0b93f920eb01488abdaefb951d7935dc</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>cbf5bb9817c420c29f32a86c</t>
@@ -2261,7 +2337,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2297,184 +2377,220 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Edison International Common Stock</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Fitch cuts Edison International outlook on wildfire reform stall</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>信用調降</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>'-0.462</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQU0w0dkdkRjBaMUxoWWZwNzBsZjg2bFItak5sSzBmNFZrVTJON2UzZmI4alFwbDEwVlV3cGlicXdFc3RLeU9HS2N3TnV4aW50cF9Ta01DRGpNd1Z1ZzdydGZZRzI5QjVYeGhPcHJXX3hNX3BpLUlla0VsSlR3ZnJzYW01MHdScW82U0s1MzlkeVJCOFh6VDdSQm5pYktlcU5sWTBtNUJXMUV0cTZhVklJRmVzem9DLVdyOWRmdTk2OE0wbnhK?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>CREDIT_DOWNGRADE</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>wildfire</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>3304740a603b4323847c8b85f3656aec</t>
+        </is>
+      </c>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>6989881c6c1300785a06d419</t>
+        </is>
+      </c>
+      <c r="AD10" s="4" t="inlineStr">
+        <is>
+          <t>bcedb6c9cb5415d5e2d85260</t>
+        </is>
+      </c>
+      <c r="AE10" s="4" t="inlineStr"/>
+      <c r="AF10" s="4" t="inlineStr"/>
+      <c r="AG10" s="4" t="inlineStr"/>
+      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr"/>
+      <c r="AL10" s="4" t="inlineStr"/>
+      <c r="AM10" s="4" t="inlineStr"/>
+      <c r="AN10" s="4" t="inlineStr"/>
+      <c r="AO10" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>'-0.462</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQU0w0dkdkRjBaMUxoWWZwNzBsZjg2bFItak5sSzBmNFZrVTJON2UzZmI4alFwbDEwVlV3cGlicXdFc3RLeU9HS2N3TnV4aW50cF9Ta01DRGpNd1Z1ZzdydGZZRzI5QjVYeGhPcHJXX3hNX3BpLUlla0VsSlR3ZnJzYW01MHdScW82U0s1MzlkeVJCOFh6VDdSQm5pYktlcU5sWTBtNUJXMUV0cTZhVklJRmVzem9DLVdyOWRmdTk2OE0wbnhK?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Investing.com</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>6989881c6c1300785a06d419</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>bcedb6c9cb5415d5e2d85260</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
+      <c r="AP10" s="4" t="inlineStr"/>
+      <c r="AQ10" s="4" t="inlineStr"/>
+      <c r="AR10" s="4" t="inlineStr"/>
+      <c r="AS10" s="4" t="inlineStr"/>
+      <c r="AT10" s="4" t="inlineStr"/>
+      <c r="AU10" s="4" t="inlineStr"/>
+      <c r="AV10" s="4" t="inlineStr"/>
+      <c r="AW10" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
+      <c r="AX10" s="4" t="inlineStr"/>
+      <c r="AY10" s="4" t="inlineStr"/>
+      <c r="AZ10" s="4" t="inlineStr"/>
+      <c r="BA10" s="4" t="inlineStr"/>
+      <c r="BB10" s="4" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="BC10" s="2" t="inlineStr">
+      <c r="BC10" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="2" t="inlineStr"/>
-      <c r="BE10" s="2" t="inlineStr">
+      <c r="BD10" s="4" t="inlineStr"/>
+      <c r="BE10" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="2" t="inlineStr">
+      <c r="BF10" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="2" t="inlineStr">
+      <c r="BG10" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
-      <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BI10" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2510,28 +2626,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2571,7 +2691,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2580,7 +2700,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>9612309ad98d40e2aa6cfeee59a835b2</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>7183580156bff63adc613a7c</t>
@@ -2601,7 +2725,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2645,10 +2773,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2684,28 +2824,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2745,7 +2889,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2754,7 +2898,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>b43431a08c4147f5b9201da699a9d53d</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>4aa27d71cd719180b7b6a112</t>
@@ -2775,7 +2923,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2819,10 +2971,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -4388,7 +4552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL6"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5168,200 +5332,192 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>JBHT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>J.B. Hunt</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-09-16T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>$167.5M Visa, Mastercard non-bank ATM class action settlement</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>J.B. Hunt shares fall Wednesday after company warns of third quarter profit decline</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>財測下修</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>'-0.543</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>'-0.961</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPUV8tNW1iOGpVMlZFV3ROZXVBRjZYYWVxSlRjNncxYXJ6Ui1YaXdrZ1V1Vzl3SC1ZM3lSWnFfZmhIT3hEZ3REV3hNUURQZFpxSEVHN3pnaFVlRGVadVNrMG93Z2oxdDVyTGlZd0JjOFZWWWhEX2tLMVVxTHNTWTByc3lJV0N3bjV5VHpUVzBlMEhKWFRSeEsxdW5ZS3FOdkh0MHVsYS1CSmpBcUJtZ1h2bW81OUtvakhpUm9GcUtBWU1ENGM1Q1Z5enVSTzdrUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t>1fd14f26f0164efc86c61a9f652b915c</t>
-        </is>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>bc205db70e8af6acd5d2bae4</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>8d7765995791c337aad27f12</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNU0s5SnRFNlRmNUxmOG94SlJmLVRWMmdzTWRrMTVIZ1hmSGllT055eXNwTUc4MnNqRC1UMGNtSWxuUXFqd2JjQzNJZkhwcFBZZGtfV0Y3TmZPSVRoUzVGV3BWR2d0WGFvWkpzN2RQZm41cHNpM3RLa2lNaUNRS0VKYWF3RTNIWlBFTGpUR2dmRVdsWnNvUFc5S3VHOXlrYlU?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>The Arkansas Democrat-Gazette</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>EARNINGS_WARNING</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>shares fall</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>b4977753ed5542b089475074f455ecd4</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>84273e6232ffb2e6c160a765</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>e98bc148db818721a897e1d9</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr"/>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>JBHT</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5534,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>GoDaddy Inc. Class A Common Stock</t>
+          <t>Edison International Common Stock</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -5393,7 +5549,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>GDDY Shareholder Alert: GoDaddy Inc. Securities Class Action Lawsuit - Investors With Losses May Contact Levi &amp; Korsinsky</t>
+          <t>Fitch cuts Edison International outlook on wildfire reform stall</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -5404,7 +5560,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>信用調降</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -5434,7 +5590,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>'-0.427</t>
+          <t>'-0.462</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -5448,44 +5604,44 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQMERnWTlnUDlWR1AxZ1dKWEszbFBCUHRJdHVleExPS0tsd3pJa1NoRXlCMEV4aENxVDNoZUMxaDlpQVBOQnRiWkU2OVhJWHBleUdINDNkdVdsOFlJanRwUmpESC04V2xra2FPenliQ1M1OUU4XzR5UEx3NU1yT210WUVRTXB6cUxlQ0F5ZDZzMVZ0LWJhM1E2SGxrbFZyd0dmU1IzR29mcmNsLXN0ZjRJTWRMeEZzYTRkZ2xuR1N4OXVhZ3BXcW5GWTJ6bGJrTXE4M0ctR3h1N2g5REgtcUZYNmNBWDQ3eHozSGk5LThrY293VWhpakNYeHJWV0pyMEk5VDVZZ3d1OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQU0w0dkdkRjBaMUxoWWZwNzBsZjg2bFItak5sSzBmNFZrVTJON2UzZmI4alFwbDEwVlV3cGlicXdFc3RLeU9HS2N3TnV4aW50cF9Ta01DRGpNd1Z1ZzdydGZZRzI5QjVYeGhPcHJXX3hNX3BpLUlla0VsSlR3ZnJzYW01MHdScW82U0s1MzlkeVJCOFh6VDdSQm5pYktlcU5sWTBtNUJXMUV0cTZhVklJRmVzem9DLVdyOWRmdTk2OE0wbnhK?oc=5</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y5" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>CREDIT_DOWNGRADE</t>
         </is>
       </c>
       <c r="Z5" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>wildfire</t>
         </is>
       </c>
       <c r="AA5" s="4" t="inlineStr"/>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>d14e0b6a3bb8446c9f5755081398ca9a</t>
+          <t>3304740a603b4323847c8b85f3656aec</t>
         </is>
       </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t>a2c9bb1d20237cde49283f51</t>
+          <t>6989881c6c1300785a06d419</t>
         </is>
       </c>
       <c r="AD5" s="4" t="inlineStr">
         <is>
-          <t>ab0f8f737ba4fa480c100a43</t>
+          <t>bcedb6c9cb5415d5e2d85260</t>
         </is>
       </c>
       <c r="AE5" s="4" t="inlineStr"/>
@@ -5521,7 +5677,7 @@
       <c r="BA5" s="4" t="inlineStr"/>
       <c r="BB5" s="4" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="BC5" s="4" t="inlineStr">
@@ -5546,7 +5702,11 @@
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="4" t="inlineStr"/>
       <c r="BK5" s="4" t="inlineStr">
         <is>
@@ -5555,7 +5715,7 @@
       </c>
       <c r="BL5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
         </is>
       </c>
     </row>
@@ -5572,12 +5732,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Mastercard Incorporated Common Stock</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5587,7 +5747,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Cintas-UniFirst deal spread widens on FTC scrutiny: Bernstein</t>
+          <t>$167.5M Visa, Mastercard non-bank ATM class action settlement</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -5598,7 +5758,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -5628,7 +5788,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>'-0.543</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -5642,12 +5802,12 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPOU9QdWY4TXZkUW1TTklzWVRQbDVlSGlZRkxhNDBWR0drM3d4Sk5pdkhFemYtM0ZZaXFvMlVQeGpfRDFhQ1ZTZXhTOHZGOEtBNWRZRG5fdklkRG5GTDBLeGpoVDdXbC01dGs1dnNiZU1sRTZwMzExeEZZd1pTeTRkYmktTzFFOU5jOG5oX3VEdkJmNVphSWxjMmF1ZEhUcGN1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPUV8tNW1iOGpVMlZFV3ROZXVBRjZYYWVxSlRjNncxYXJ6Ui1YaXdrZ1V1Vzl3SC1ZM3lSWnFfZmhIT3hEZ3REV3hNUURQZFpxSEVHN3pnaFVlRGVadVNrMG93Z2oxdDVyTGlZd0JjOFZWWWhEX2tLMVVxTHNTWTByc3lJV0N3bjV5VHpUVzBlMEhKWFRSeEsxdW5ZS3FOdkh0MHVsYS1CSmpBcUJtZ1h2bW81OUtvakhpUm9GcUtBWU1ENGM1Q1Z5enVSTzdrUQ?oc=5</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Top Class Actions</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr"/>
@@ -5658,28 +5818,28 @@
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>FTC</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr"/>
       <c r="AB6" s="4" t="inlineStr">
         <is>
-          <t>91e5816a488044f7855b55c4234c4808</t>
+          <t>1fd14f26f0164efc86c61a9f652b915c</t>
         </is>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t>36670ce2603c548a0270fcbb</t>
+          <t>bc205db70e8af6acd5d2bae4</t>
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>9f5ec405fcd4176d62c2d489</t>
+          <t>8d7765995791c337aad27f12</t>
         </is>
       </c>
       <c r="AE6" s="4" t="inlineStr"/>
@@ -5706,7 +5866,7 @@
       <c r="AV6" s="4" t="inlineStr"/>
       <c r="AW6" s="4" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="AX6" s="4" t="inlineStr"/>
@@ -5715,7 +5875,7 @@
       <c r="BA6" s="4" t="inlineStr"/>
       <c r="BB6" s="4" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="BC6" s="4" t="inlineStr">
@@ -5726,12 +5886,12 @@
       <c r="BD6" s="4" t="inlineStr"/>
       <c r="BE6" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
       <c r="BF6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
       <c r="BG6" s="4" t="inlineStr">
@@ -5740,7 +5900,11 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="4" t="inlineStr"/>
       <c r="BK6" s="4" t="inlineStr">
         <is>
@@ -5753,8 +5917,396 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc. Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>GDDY Shareholder Alert: GoDaddy Inc. Securities Class Action Lawsuit - Investors With Losses May Contact Levi &amp; Korsinsky</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.427</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQMERnWTlnUDlWR1AxZ1dKWEszbFBCUHRJdHVleExPS0tsd3pJa1NoRXlCMEV4aENxVDNoZUMxaDlpQVBOQnRiWkU2OVhJWHBleUdINDNkdVdsOFlJanRwUmpESC04V2xra2FPenliQ1M1OUU4XzR5UEx3NU1yT210WUVRTXB6cUxlQ0F5ZDZzMVZ0LWJhM1E2SGxrbFZyd0dmU1IzR29mcmNsLXN0ZjRJTWRMeEZzYTRkZ2xuR1N4OXVhZ3BXcW5GWTJ6bGJrTXE4M0ctR3h1N2g5REgtcUZYNmNBWDQ3eHozSGk5LThrY293VWhpakNYeHJWV0pyMEk5VDVZZ3d1OA?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>d14e0b6a3bb8446c9f5755081398ca9a</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>a2c9bb1d20237cde49283f51</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>ab0f8f737ba4fa480c100a43</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="BC7" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Cintas Corporation</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Cintas-UniFirst deal spread widens on FTC scrutiny: Bernstein</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>0.258</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPOU9QdWY4TXZkUW1TTklzWVRQbDVlSGlZRkxhNDBWR0drM3d4Sk5pdkhFemYtM0ZZaXFvMlVQeGpfRDFhQ1ZTZXhTOHZGOEtBNWRZRG5fdklkRG5GTDBLeGpoVDdXbC01dGs1dnNiZU1sRTZwMzExeEZZd1pTeTRkYmktTzFFOU5jOG5oX3VEdkJmNVphSWxjMmF1ZEhUcGN1?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>91e5816a488044f7855b55c4234c4808</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>36670ce2603c548a0270fcbb</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>9f5ec405fcd4176d62c2d489</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
+      <c r="BC8" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG8" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BL6"/>
+  <autoFilter ref="A1:BL8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
